--- a/data/dividends_info_20260509.xlsx
+++ b/data/dividends_info_20260509.xlsx
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>27.35000038146973</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I48" t="n">
-        <v>4.058500857470011</v>
+        <v>4.051094946911317</v>
       </c>
       <c r="J48" t="n">
         <v>26</v>
@@ -9628,7 +9628,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9645,7 +9645,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9662,7 +9662,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9689,14 +9689,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9713,7 +9713,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9730,7 +9730,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9798,7 +9798,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9883,7 +9883,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9893,14 +9893,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9910,14 +9910,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9927,14 +9927,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9944,14 +9944,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9961,14 +9961,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9995,14 +9995,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10012,14 +10012,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10036,7 +10036,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10172,7 +10172,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10199,14 +10199,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10223,7 +10223,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10240,7 +10240,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10250,14 +10250,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10267,14 +10267,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10284,14 +10284,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10301,14 +10301,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10318,14 +10318,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10335,14 +10335,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10352,14 +10352,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10369,14 +10369,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10393,7 +10393,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10403,14 +10403,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10427,7 +10427,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10437,14 +10437,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10454,14 +10454,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10478,7 +10478,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10495,7 +10495,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10512,7 +10512,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10522,14 +10522,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10546,7 +10546,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10563,7 +10563,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10580,7 +10580,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10590,14 +10590,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10607,14 +10607,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10631,7 +10631,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10648,7 +10648,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10665,7 +10665,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10733,7 +10733,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10750,7 +10750,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10767,7 +10767,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10777,14 +10777,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10818,7 +10818,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10835,7 +10835,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10845,14 +10845,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10869,7 +10869,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10903,7 +10903,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10920,7 +10920,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10954,7 +10954,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10988,7 +10988,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10998,14 +10998,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11015,14 +11015,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11032,14 +11032,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11049,14 +11049,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11073,7 +11073,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11090,7 +11090,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11107,7 +11107,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11117,14 +11117,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11141,7 +11141,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11151,14 +11151,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11168,14 +11168,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -11202,14 +11202,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11219,14 +11219,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11243,7 +11243,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11253,14 +11253,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11277,7 +11277,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11287,14 +11287,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11304,14 +11304,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11328,7 +11328,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11338,14 +11338,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11362,7 +11362,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11372,14 +11372,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11389,14 +11389,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11406,14 +11406,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11430,7 +11430,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11440,14 +11440,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11457,14 +11457,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11474,14 +11474,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11491,14 +11491,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11508,14 +11508,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11525,14 +11525,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11542,14 +11542,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11566,7 +11566,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11576,14 +11576,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11593,14 +11593,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11617,7 +11617,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11634,7 +11634,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11712,14 +11712,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11729,14 +11729,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11814,14 +11814,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11831,14 +11831,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11855,7 +11855,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11865,14 +11865,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11882,14 +11882,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11906,7 +11906,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11923,7 +11923,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11933,14 +11933,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11950,14 +11950,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -11991,7 +11991,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12001,14 +12001,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12018,14 +12018,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12035,14 +12035,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12052,14 +12052,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12069,14 +12069,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12086,14 +12086,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12110,7 +12110,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12127,7 +12127,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12137,14 +12137,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12161,7 +12161,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12178,7 +12178,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12195,7 +12195,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12205,14 +12205,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12229,7 +12229,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12239,14 +12239,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12256,14 +12256,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12280,7 +12280,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12290,14 +12290,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12382,7 +12382,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12392,14 +12392,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12409,14 +12409,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12426,14 +12426,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12443,14 +12443,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12467,7 +12467,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12477,14 +12477,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12494,14 +12494,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12518,7 +12518,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12535,7 +12535,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12545,14 +12545,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12569,7 +12569,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12579,14 +12579,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12596,14 +12596,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12637,7 +12637,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12647,14 +12647,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12671,7 +12671,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12688,7 +12688,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12705,7 +12705,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12715,14 +12715,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12732,14 +12732,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12756,7 +12756,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12766,14 +12766,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12790,7 +12790,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12807,7 +12807,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12824,7 +12824,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12834,14 +12834,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12875,7 +12875,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12885,14 +12885,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12909,7 +12909,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12943,7 +12943,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12953,14 +12953,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12977,7 +12977,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13147,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13164,7 +13164,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13202,61 +13202,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>E.P.H. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TRAWELL CO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>